--- a/03_coding/coding_evidence.xlsx
+++ b/03_coding/coding_evidence.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coding Evidence" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding_Evidence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,21 +27,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,8 +51,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -429,23 +422,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="29.7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14.4" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26.1" customWidth="1" min="10" max="10"/>
+    <col width="64.8" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10.8" customWidth="1" min="14" max="14"/>
+    <col width="19.8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,330 +455,5733 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>quote_or_paraphrase</t>
+          <t>page_as_recorded</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>segment_verbatim</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>coding_decision</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_v1_workbook</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_published_etecom2026</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>published_evidence_etecom2026</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>revision_note</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>coder</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>coding_date</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>second_coder</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>second_coder_agreement</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>resolution_notes</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>linked_synthesis_theme</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EV-0001</t>
+          <t>EV-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>STU-0001</t>
+          <t>STU-09</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COD-01</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>4</v>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>3.1 Identity Federation</t>
+          <t>D1.1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE quote: "We propose a federated identity broker that maps provider-native IAM roles to a canonical policy schema."</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>paper addresses "information security governance" as a general organisational domain; no multi-cloud or cross-provider context addressed (p.1; abstract).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE Coder A</t>
+          <t>No multi-cloud or cross-provider architecture content → No.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder B</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Agree</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE: Cross-provider identity federation</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EV-0002</t>
+          <t>EV-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>STU-0001</t>
+          <t>STU-08</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COD-03</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>7</v>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4.2 Unified Audit Logging</t>
+          <t>D1.3</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE paraphrase: the authors describe aggregating CloudTrail- and Azure-Monitor-style logs into a single schema for cross-cloud audit.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>paraphrase</t>
+          <t>"This review comprehensively examines the critical security and privacy concerns associated with multi-cloud and hybrid cloud architectures" (abstract, p.1).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE Coder A</t>
+          <t>Explicitly multi-cloud and hybrid-cloud framed → Yes.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>TEMPLATE Coder B</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Disagree</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE: second coder felt this was closer to COD-02; resolved by discussion, kept as COD-03.</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE: Lack of standardized audit trails</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EV-0003</t>
+          <t>EV-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>STU-0002</t>
+          <t>STU-04</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COD-02</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3</v>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 Related Work</t>
+          <t>D1.1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE quote: "Existing policy engines are provider-specific and do not generalize to multi-cloud deployments."</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>paper provides "a comprehensive analysis of the current state of the art in cybersecurity risk assessment, governance, and compliance" across 24 models (p.136); no multi-cloud or cross-provider architecture addressed.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE Coder A</t>
+          <t>General cybersecurity governance scope; no multi-cloud framing → No.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Not double-coded</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Not double-coded</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE: Policy fragmentation across providers</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EV-0004</t>
+          <t>EV-004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>STU-0002</t>
+          <t>STU-07</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COD-04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>9</v>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5 Discussion, Table 2</t>
+          <t>D1.3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE (table): Table 2 lists "no cross-cloud compliance reporting standard" as an open gap identified by the authors.</t>
+          <t>57792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>"in this SLR, we have reviewed the literature on cloud computing topics, including cloud security threats and their mitigation strategies."; "examined the research studies published between 2010 and 2020" (p.57792);</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE Coder A</t>
+          <t>Cloud environments addressed broadly; multi-cloud not the explicit frame but cross-provider threats included → Partial.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Not double-coded</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Not double-coded</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>EXAMPLE: No vendor-neutral compliance reporting standard</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EV-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>"While this is our recommendation, we also understand that many CSCs are forced to support multi-cloud before reaching the expected maturity level" (CSA, 2021, p.98); multi-cloud acknowledged conceptually in Domains 3-4 as advisory guidance.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud acknowledged conceptually but no prescriptive cross-provider governance requirements defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Partial*</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Domains 3-4</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Organized around seven core topics, Authentication and Authorization, Identity Verification and Risk Management, Attribute Management, Security and Privacy, Audit and Compliance, User Lifecycle Management, and Interoperability and Federation, this study provides "this study provides a detailed examination of these aspects particularly to achieve robust security, privacy, and interoperability across multi- loud platforms." organised around seven core IAM topics (p.6224).</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud IAM explicitly the stated focus and context of the survey → Yes.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>EV-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70006</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>"This study uses a systematic literature review methodology adopting the Kitchenham method, which includes a literature search across leading academic databases including IEEE Xplore, ScienceDirect, ACM, SpringerLink, Emerald Insight, Nature, Taylor &amp; Francis, Scopus, and ProQuest. A formal protocol was followed to conduct an automated search of relevant articles published between 2021 and 2024, and filters were applied. Based on the initial search results, 2038 studies were found, then the selection criteria process (inclusion and exclusion) and quality assessment were carried out, and finally 30 studies were selected for further research."  (p.70006).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly multi-cloud scoped systematic review → Yes.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EV-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>paper evaluates "ISO/IEC 27001 and 27002, FedRAMP, and SOC 2 against a third-party benchmark, the Cloud Controls Matrix" (p.1); no multi-cloud or cross-provider architecture addressed.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Single-cloud coverage mapping only; no multi-cloud framing → No.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>EV-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>standard is architecture-agnostic; A.5.23 addresses "Information security for use of cloud services" but does not distinguish between single-provider and multi-provider architecture (Annex A, p.12).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>No multi-cloud or cross-provider specificity → No.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Cloud services addressed generically (A.5.23); no multi-cloud provisions</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EV-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>D1.4</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>paper proposes "The Multi-Cloud Security Model brings inter-server
+verbal exchange, authentication integrity"; study "The primary goal of this investigation is to create a safe architecture for inter-server communication within multi-cloud systems". (Introduction)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud environment is the explicit experimental context → Yes.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EV-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>"The CSF is designed to be used by organizations of all sizes and sectors, including industry, government, academia, and nonprofit organizations, regardless of the maturity level of their cybersecurity programs." (NIST, 2024, p.2); GV.SC addresses supply chain and cloud provider relationships generically, "GV.SC-01: A cybersecurity supply chain risk management program, strategy, objectives, policies, and processes are established and agreed to by organizational stakeholders" (NIST, 2024, p.17), without distinguishing single-provider from multi-provider governance requirements.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Framework is architecture-agnostic by explicit design; no subcategory specifies governance requirements for concurrent multi-provider deployment → No.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Architecture-agnostic</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>EV-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>"This document presents cloud access control (AC) characteristics and a set of general access control guidance for cloud service models-IaaS (Infrastructure as a Service), PaaS (Platform as a Service), and SaaS (Software as a Service)" (p. iv).</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Single cloud service model scope only; no multi-cloud or cross-provider context; D1 = No.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Sec. 6 (inter-provider operation)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Coverage revised during ETECOM 2026 author review: No -&gt; Partial; original first-coder rating kept in coverage_v1_workbook.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EV-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>paper presents a "Reference Service Model for Federated Identity Management" - provider-heterogeneous deployment not stated; model is architecturally provider-agnostic (p.196).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No multi-cloud architecture context; federation model is provider-agnostic in design → No.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EV-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>D1.4</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>"we used the Kill Chain attack model for our implementation to determine the tactics, techniques, and procedures (TTP) used by cyberattacks to exploit the multi-cloud environment" (p. 218).</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly multi-cloud lab (Azure Arc, AWS EKS, GCP Anthos); D1 = Yes - empirical multi-cloud focus confirmed.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EV-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>"the review identified the need for developing a holistic framework for the information security governance that (1) connects the organization's objectives and its protection, (2) addresses each aspect of strategy, control, and regulation, (3) ensures compliance of procedures and guidelines with policies, and (4) ensures continuous evaluation and compliance" (p.28).</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Explicit, complete information security governance framework with four defined structural components → Yes.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EV-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>paper provides "We analyze existing security strategies, including cryptographic techniques, identity and access management (IAM) mechanisms, AI-driven threat detection, and privacy-preserving methodologies. Furthermore, we provide a comparative evaluation of these approaches, highlighting their trade-offs in terms of security effectiveness, computational overhead, and deployment feasibility". it is covering IAM, data security, network security, regulatory compliance (abstract, p.1).</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Broad governance analysis with comparative structure across multiple security domains → Yes.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EV-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>"The evaluation framework (shown in Figure 1) is based on nine essential metrics that collectively provide a comprehensive assessment of cybersecurity risk assessment, governance, and compliance models. Privacy measurement... performance... precision... ethics... customisation... integration capabilities... resilience... automation levels... cost evaluations" (p.139).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive structured governance evaluation across 24 models and 9 metrics → Yes.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EV-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>57805</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>"in this SLR, we have reviewed the literature on cloud computing topics, including cloud security threats and their mitigation strategies" (p.57805); paper produces a three-level threat taxonomy (Fig. 6, p.57802) classifying threats without defining governance frameworks, oversight mechanisms, or accountability structures.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is threat identification and mitigation classification; no governance framework or structure content → No.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EV-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Domain 2 provides "cloud governance" covering policies, procedures, roles, and compliance, and the relationship between CSP and CSC (CSA, 2021, p.28).</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Cloud governance explicitly addressed as a domain; D2 → Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Domain 2</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>EV-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>"Federated identity management solutions, on the other hand, have the ability to offer permission and authentication across systems" - governance requirements for federation identified as requiring cross-provider establishment but no governance framework structure defined (p.6224).</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Governance referenced conceptually in the federation context; no complete governance framework or structure provided → Partial.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>EV-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>70006</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>"The security challenges in multi-cloud environments arise from the variability of security policies and standards among providers, resulting in configuration inconsistencies, complex authorization processes, and heightened risks of security breaches" (p.70006).</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Governance challenges documented thematically; no governance framework or structure defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>EV-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>"FedRAMP Rev. 5, provided the highest alignment in coverage to CCM v4, with 94% of controls found in CCM having full coverage. ISO/IEC 27001/02:2022 provided the second highest alignment in coverage to CCM v4, with 61% of controls fully covered. SOC 2 had the lowest number of controls with full coverage, with only 28%" (p.5).</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Structured quantitative governance coverage evaluation across three frameworks → Yes.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EV-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ISMS structure "Clauses 4 (Context of the organization), 5 (leadership), 6 (planning), 7 (support), 8 (operation), 9 (performance evaluation), 10 (improvement)" provide a complete auditable governance management system (Clauses 4-10, pp.1-10).</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Full, auditable governance management system structure with defined clauses → Yes.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Clauses 4.1-4.3, 5.1, 6.1, 9.3</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EV-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>"The primary goal of this investigation is to create a safe architecture for inter-server communication within multi-cloud systems" (Introduction); paper proposes and benchmarks SIDH, Blowfish, RSA, and BLAKE2 cryptographic algorithms for authentication performance - "overall execution time is 94.5 in SSCA and 55 in SIDH" (Results).</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is confined to cryptographic authentication benchmarking; no governance framework, policy structure, role definition, or oversight mechanism is defined anywhere in the paper → No.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EV-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>GOVERN function defines subcategories "GV.OC (organisational context), GV.RM (risk management strategy), GV.RR (Roles, Responsibilities, and Authorities), GV.PO (policy), GV.OV (oversight), GV.SC (Cybersecurity Supply Chain Risk Management)" (NIST, 2024, p.16).</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Dedicated governance function with defined subcategories covering full governance management scope → Yes.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>GV.OC, GV.RM, GV.OV</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>EV-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>D2.PO</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>"guidance for AC system for each cloud service model, as described in Sections 3, 4, and 6 of this document, can be further extended to system requirements by referring to the AC control elements listed in NIST SP 800-53" (p. 7).</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Governance addressed as access control policy structure for individual service models; not a complete multi-cloud governance framework; D2 = Partial.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Secs. 3.3, 5.7 (policy guidance only)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EV-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>"the need for a holistic architecture view is mandatory to avoid duplication in realization and to obtain synergy effects between the different systems. Especially the collaboration of several institutions in a federation becomes a challenge due to the growing IT complexity and architecture as a whole" (p. 200).</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Governance referenced at the conceptual architectural level for federated identity management; no complete cloud governance framework structure defined; D2 = Partial.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>EV-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>"the key challenge and complexities associated with managing multi-cloud environments, particularly regarding governance, security, resource fragmentation, and compliance, is establishing effective governance practices" (p. 220).</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Governance named as the primary challenge category; D2 = Yes.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>EV-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>framework "ensures compliance of procedures and guidelines with policies" as one of its four structural components (abstract, p.1).</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Policy compliance addressed as a governance element; no cloud-specific enforcement mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>EV-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>"Identity management across several cloud providers demands IAM systems that deliver uniform identity services between multiple providers who maintain separate authentication protocols and authorization policies" (p.11).</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Policy enforcement requirements identified at cross-provider level; no prescriptive enforcement mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>EV-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>compliance scope assessed across frameworks - "Expanding compliance scope to create unified frameworks that help organizations efficiently navigate the complex web of security regulations is another key priority" (p.139).</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Policy governance addressed as evaluation dimension; no specific policy enforcement mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>EV-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>57799</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>"Firewall configuration, server patching, and placement of the intrusion-detection system are enforced. The use of encryption and authentication processes can ensure data availability and con_x001C_dentiality" (p. 57799).</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Access control and authentication identified as security threat categories; policy enforcement addressed indirectly through threat identification; no enforcement mechanism defined → D3 = Partial.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>EV-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Domain 2 (CSA, 2021, p.28) and Domain 5 (CSA, 2021, p.103) address policy governance and IAM policy enforcement in cloud contexts.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Policy enforcement addressed through dedicated domain-level provisions → Yes.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Domains 2, 5</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>EV-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>"Organized around seven core topics, Authentication and Authorization, Identity Verification and Risk Management, Attribute Management, Security and Privacy, Audit and Compliance, User Lifecycle Management, and Interoperability and Federation, this study provides "this study provides a detailed examination of these aspects particularly to achieve robust security, privacy, and interoperability across multi- loud platforms."  (p.6223) survey scope is IAM taxonomy; policy enforcement not addressed as a distinct governance mechanism in any of the seven topic areas.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>No policy enforcement content → No.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>EV-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>70006</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>"most of the multi-cloud security issue trends fall into the areas of data, cryptography, authentication and authorization" (p.70006); "authentication and authorization" identified as dominant challenge category across reviewed papers (p.70012).</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Policy enforcement challenges documented through literature synthesis; no enforcement mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EV-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>policy enforcement coverage inferred from overall CCM control coverage percentages (p.4-5); "CCM v4 encapsulates a holistic approach to risk management" (p.5) but Hegde does not isolate policy enforcement as an independent result.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Policy enforcement addressed indirectly through CCM coverage mapping; no standalone enforcement mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>EV-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Annex A control "A.5.23 Information security for use of cloud services" (p.12); "A.8.9 configuration management" (p. 16); Clause "5.2 policy (p.3).</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Specific enforceable policy controls defined at clause and Annex A control level → Yes.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Clauses 5.2, 8.1; A.5.1, A.8.9</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>EV-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>"The primary goal of this investigation is to create a safe architecture for inter-server communication within multi-cloud systems" (Introduction); paper output is a performance comparison of authentication algorithms - "The achieved response time is 3.85 in SSCA and 2.01 in SIDH" (Results).</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Paper contributes a cryptographic performance benchmark, not a policy enforcement mechanism; no cloud policy definition, enforcement control, or compliance procedure is addressed → No.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>EV-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>"GV.PO-01: Policy for managing cybersecurity risks is established based on organizational context" and "GV.PO-02: Policy for managing cybersecurity risks is reviewed, updated, communicated, and enforced" (NIST, 2024, p.17).</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Explicit policy enforcement requirements with defined governance obligations → Yes.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>GV.PO-01/02, PR.PS-01/06</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>EV-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>"attribute-based access control (ABAC) [24] and attribute-based encryption (ABE) schemes can be used to control access to SaaS data [23, 25, 26, 27, 28] since these schemes can use the identity of users through attributes to manage, encrypt, and decrypt application data" (p. 14).</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Explicit cloud authorisation enforcement mechanism (ABAC) defined and operationalised across IaaS/PaaS/SaaS service models; D3 = Yes.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Secs. 3.5, 4.3, 5.7, 5.9, 6</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>EV-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>paper presents a "Reference Service Model for Federated Identity Management" (p.196); the FIMSM defines six architectural layers via ArchiMate: "reference architecture FIMSM, using different layers to differentiating roles from business, applications, and technology. The reference architecture includes external layer, business service layer, business layer, application service layer, application layer, and the technical service layer." (p.201), all addressing identity federation architecture rather than policy enforcement controls.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Paper output is a federated identity architectural reference model; no policy enforcement mechanism, governance control, or compliance obligation is defined → No.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>EV-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>"resource provisioning, access control, and compliance policies must be aligned across multi-cloud environments, yet differences in provider-specific controls can hinder policy uniformity" (p. 220).</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Policy alignment challenge identified but no enforcement mechanism defined; D3 = Partial.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>EV-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>"The systematic literature review presented in this paper aims to introduce information security governance as a comprehensive solution for alignment between information security policies and the organization's objectives" (p.1); the four governance framework components defined are: "To the best of our knowledge, the review identified the need for developing a holistic framework for the information se- curity governance that (1) connects the organization’s objec- tives and its protection, (2) addresses each aspect of strat- egy, control, and regulation, (3) ensures compliance of proce- dures and guideline with policies, and (4) ensures continuous evaluation and compliance" (p.28), none address cloud provider-customer shared responsibility boundaries.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is organisational ISMS governance; cross-provider shared responsibility allocation is absent from all seven governance domains and 27 critical success factors → No.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>EV-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>"the selection process more challenging when organizations need to decide between role-based access control (RBAC) and attribute-based access control (ABAC)" (p.11) - "Table 2: Comparison of security and privacy challenges in multi-cloud and hybrid cloud environments." documents "RBAC vs. ABAC selection" : "RBAC lacks flexibility, ABAC is complex to manage" as a core IAM challenge. (P.13).</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Accountability ambiguity at cross-provider IAM level explicitly documented; no resolution mechanism specified → Partial.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>EV-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>shared responsibility not among the nine assessment metrics - metrics are: "Privacy measurement... performance... precision... ethics... customisation... integration capabilities... resilience... automation levels... cost evaluations" (p.139).</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>No shared responsibility or accountability boundary content → No.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>EV-046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>57805</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>"in this SLR, we have reviewed the literature on cloud computing topics, including cloud security threats and their mitigation strategies" (p.57805); the three-level threat taxonomy (Fig. 6, p.57802) classifies attack categories without including shared responsibility or provider-customer accountability boundaries as a reviewed dimension.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility boundary allocation is not a threat category in the taxonomy; accountability content entirely absent → No.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>EV-047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>"This is commonly referred to as the Shared Security Responsibility Model (SSRM), sometimes shortened to SRM. Think of it as a responsibility matrix that depends on the particular cloud provider and feature/product, service, and deployment model." - disaggregated across IaaS, PaaS, SaaS (CSA, 2021, p.21).</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SSRM explicitly defined across IaaS/PaaS/SaaS; D4 → Yes.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Domain 1</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>EV-048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is an IAM governance taxonomy structured around seven topics: "Authentication and Authorization, Identity Verification and Risk Management, Attribute Management, Security and Privacy, Audit and Compliance, User Lifecycle Management, and Interoperability and Federation" (p.6223); no content addressing provider-customer accountability boundaries or cross-provider shared responsibility allocation appears in any of the seven topic areas.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>No shared responsibility content → No.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>EV-049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>70006</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>"The security challenges in multi-cloud environments arise from the variability of security policies and standards among providers" creating cross-provider accountability gaps (p.70006).</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility challenges referenced as a primary challenge area; no accountability boundary allocation mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>EV-050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>"there is an evident need for comprehensive guidance on the applicability of a shared security responsibility model (SSRM) throughout the supply chain" identified as a primary gap between CCM and FedRAMP (p.5).</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility gap identified; not analysed as a cross-provider accountability mechanism → Partial.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>EV-051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>"A.5.23  Information security for use of cloud services" addresses shared responsibility in the context of cloud service use (Annex A, p. 12); Clause "5.3 Organizational roles, responsibilities and authorities" defines roles and responsibilities (p.3).</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility addressed at single-provider level through ISMS role provisions and A.5.23; no cross-provider boundary coordination mechanism → Yes (single-provider scope only).</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Clause 5.3; A.5.23</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>EV-052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>"The primary goal of this investigation is to create a safe architecture for inter-server communication within multi-cloud systems" (Introduction); paper scope is inter-server authentication integrity via SIDH and ABE-OD mechanisms with no discussion of security obligation allocation between provider and customer.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Paper does not engage with shared responsibility boundaries or cross-provider accountability allocation in any section; D4 = No.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>EV-053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>"GV.RR" defines "Roles, Responsibilities, and Authorities"; "GV.SC-01: A cybersecurity supply chain risk management program, strategy, objectives, policies, and processes are established and agreed to by organizational stakeholders" covering cloud provider relationships (NIST, 2024, p.17).</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility and cross-provider relationship governance addressed through defined subcategories → Yes.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>GV.RR, GV.SC</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>EV-054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>"this document focuses on providing guidance for access control systems that are applicable to an organisation's cloud implementation and security management. It does not prescribe the internal cloud access control standards that an organisation may need in their enterprise systems or within a community other than the organisation itself" (p. 1).</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>- responsibility boundary governance not addressed; document focuses on customer-side access control only; D4 = No.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Sec. 2 (shared access-control responsibility)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Coverage revised during ETECOM 2026 author review: No -&gt; Partial; original first-coder rating kept in coverage_v1_workbook.</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>EV-055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>"Providers like Google allow users to securely reuse their accounts to authenticate at other services by utilizing the protocols Open Authorization (OAuth)/OpenID Connect (OIDC). The alternative Federated Identity Management (FIM) protocol Security Assertion Markup Language (SAML) is typically used in research and education" (p.196); paper scope is protocol-level federation architecture with no discussion of provider vs. customer security obligation allocation.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Shared responsibility boundary definition between cloud provider and customer is not referenced anywhere in the paper; scope is limited to identity protocol architecture → No.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>EV-056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>"managing user identities and access controls consistently across multi-cloud environments also presents challenges, as IAM configurations must align with organisational requirements while accommodating the nuances of various cloud providers' IAM models" (p. 220).</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Cross-provider IAM misalignment documented; no cross-provider SRM defined; D4 = Partial.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>EV-057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>D5.X</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>framework "addresses each aspect of strategy, control, and regulation"; "The review identified seven information security governance domains with 27 critical success factors" including risk-relevant components. (abstract, p.1)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Risk governance present as a framework element; no cloud-specific risk posture management mechanism → Partial.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>EV-058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>"we provide a comparative evaluation of these approaches, highlighting their trade-offs in terms of security effectiveness, computational overhead, and deployment feasibility" including CSPM and AI-driven threat detection (abstract, p.1).</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Risk posture tools reviewed comparatively; no unified cross-provider risk posture framework defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>EV-059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>"resilience indicates the model's effectiveness under varying conditions" - one of the nine evaluation metrics (p.139); risk quantification assessed for each of 24 models (p.140).</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Risk elements present within the evaluation framework; no dedicated cloud risk posture management mechanism → Partial.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>EV-060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>57803</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>"this paper provides a substantial growing literature on cloud computing security challenges, commercial cloud services providers, cloud consumers' concerns, and blockchain technology. The proposed taxonomy, as shown in Fig. 6, is based on three levels" (p. 57803).</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Taxonomy of cloud security threats provides a risk-identification basis across 71 studies; no continuous risk posture monitoring or cross-provider aggregation mechanism defined → D5 = Partial.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>EV-061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>"CSPM are tools and practices that help organizations continuously monitor, assess, and improve the security status of their cloud infrastructure" - Domain 6 covers CSPM, logging, monitoring, and incident response (CSA, 2021, p.129).</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>CSPM addressed as a dedicated governance domain with specific provisions → Yes.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Domain 6</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>EV-062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is an IAM governance taxonomy structured around seven topics: "Authentication and Authorization, Identity Verification and Risk Management, Attribute Management, Security and Privacy, Audit and Compliance, User Lifecycle Management, and Interoperability and Federation" (p.6223); no content addressing cloud security posture management, continuous monitoring, or cross-provider risk posture aggregation appears in any of the seven topic areas.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>No risk posture management content → No.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>EV-063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>70016</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>"virtualization, confidential computing and service availability still have aspects that can be explored further for future research" (p. 70016); unified threat detection and cross-CSP coordination identified as open research areas.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Risk posture gaps across providers identified as a primary unresolved area; D5 = Yes.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>EV-064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>frameworks evaluated against "Treacherous Twelve" cloud computing threats; "ISO/IEC 27001/02 and FedRAMP adequately address insufficient identity and credential management, insecure interfaces, misconfiguration, cloud strategy gaps" (p.5).</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Risk posture partially covered through threat-mapping evaluation; no dedicated cross-provider risk posture mechanism → Partial.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>EV-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Clause "6.1 Actions to address risks and opportunities" mandates risk identification, analysis, and evaluation as part of ISMS planning (p.3).</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Risk assessment required by standard; no cloud-specific or cross-provider risk posture monitoring mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>A.8.9</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>EV-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>"The achieved response time is 3.85 in SSCA and 2.01 in SIDH" - benchmark comparing proposed SIDH authentication against SSCA (Scalable and Secure Cloud Architecture) in simulated multi-cloud environment; "overall execution time is 94.5 in SSCA and 55 in SIDH" (Table 5 results section).</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Authentication risk posture assessed empirically through quantitative benchmarking in multi-cloud context → Yes.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>EV-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>"Continuous Monitoring (DE.CM)" DE.CM-01 through DE.CM-09 continuous monitoring subcategories (NIST, 2024, p.21); "Risk Assessment (ID.RA)" ID.RA-01 through ID.RA-10 risk assessment subcategories (NIST, 2024, p.18).</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive risk posture governance through dedicated DETECT and IDENTIFY function subcategories → Yes.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>ID.RA-01-10, DE.CM-01-09</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>EV-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>"Resource usage is monitored, controlled, and reported to provide transparency to both the provider andconsumer of the utilized service. To maintain resource usage, cloud consumers should beauthorized to review but not to modify their own metering data since this could lead to thefalsification of payments required for cloud services." (p. 7).</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Risk posture monitoring addressed at individual service model level through metering; not cross-provider aggregation; D5 = Partial.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Out of scope (Executive Summary)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Coverage revised during ETECOM 2026 author review: Partial -&gt; No; original first-coder rating kept in coverage_v1_workbook.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>EV-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>"Providers like Google allow users to securely reuse their accounts to authenticate at other services by utilizing the protocols Open Authorization (OAuth)/OpenID Connect (OIDC). The alternative Federated Identity Management (FIM) protocol Security Assertion Markup Language (SAML) is typically used in research and education" (p.196).</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Paper scope is federated identity reference architecture; cloud security posture management, continuous monitoring, and risk posture aggregation are not referenced in any section of the paper → No.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>EV-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>D5.X</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>attack simulation reveals cross-provider risk gaps "coordinating security policies and best practices across multiple cloud providers poses a significant challenge, as each provider offers its own set of security services and features" (p. 220).</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Empirical cross-provider risk posture gap demonstrated; D5 = Partial.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>EV-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>"The review identified seven information security governance domains with 27 critical success factors" (p.1); domains cover: "To the best of our knowledge, the review identified the need for developing a holistic framework for the information se- curity governance that (1) connects the organization’s objec- tives and its protection, (2) addresses each aspect of strat- egy, control, and regulation, (3) ensures compliance of proce- dures and guideline with policies, and (4) ensures continuous evaluation and compliance" (p.28) with no reference to identity management, access management, or IAM federation among the seven domains or 27 factors.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Identity management and federated IAM are entirely absent from the enumerated governance domains and critical success factors; no IAM federation governance content → No.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>EV-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>"Identity management across several cloud providers demands IAM systems that deliver uniform identity services between multiple providers" (p.11); "federated identity, Single Sign-On (SSO)" recommended in "Table 2" as mitigation strategy (p.13).</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>IAM addressed with cross-provider framing; no complete cross-provider IAM federation governance mechanism defined → Partial.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>EV-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>IAM federation not among the nine evaluation metrics; "federated learning models achieve the highest privacy rating" (p.136) but this refers to federated machine learning for privacy, not IAM federation governance.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>No IAM or identity federation governance content → No.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>EV-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>57805</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>"in this SLR, we have reviewed the literature on cloud computing topics, including cloud security threats and their mitigation strategies" (p.57805); identity management appears only as a sub-item of access control threats - "The use of encryption and authentication processes can ensure data availability and confidentiality" (p.57799), not as a federated identity governance dimension.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>IAM federation governance (cross-provider identity trust, protocol interoperability, lifecycle synchronisation) is not addressed; identity appears only as a technical threat subcategory → No.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>EV-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>"Identity Federation establishes the relationship between an IdP, which handles authentication, and an RP where authorizations are managed. In the cloud, the RP is typically a cloud service or application" (CSA, 2021, p.107); Domain 5 specifies requirements for federating across multiple CSPs.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Federated IAM addressed as an explicit governance domain; most cloud-contextualised IAM guidance in the corpus → Yes.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Domain 5</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>EV-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>"Organized around seven core topics, Authentication and Authorization, Identity Verification and Risk Management, Attribute Management, Security and Privacy, Audit and Compliance, User Lifecycle Management, and Interoperability and Federation"  (p.6223) - providing "a detailed examination to achieve robust security, privacy, and interoperability across multi-Cloud platforms" (p.6224).</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive IAM federation taxonomy with explicit cross-provider interoperability and federation dimension → Yes.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>EV-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>70012</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>"data security, encompassing cryptography, together with authentication and authorization, are the most commonly addressed topics" (p. 70012).</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Authentication and authorization grouped as a technical security issue area, not as a federation governance dimension; no cross-provider IAM federation governance content identified; D6 = No.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>EV-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>IAM partially covered - "the highest coverage of mitigating controls was found against the 'Insecure Interfaces and APIs' risk category because SOC 2 contains many of the same identity and access management (IAM) controls" (p.5).</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>IAM addressed within CCM coverage scope; no cross-provider IAM federation mechanism evaluated → Partial.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>EV-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Annex A controls "A.5.15-A.5.18" address access control, identity management and authentication applicable to any IT environment; no multi-provider federation distinction (p.12).</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>IAM addressed through Annex A controls; no cross-provider federation governance mechanism → Partial.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>A.5.15-A.5.18</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>EV-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>"The proposed SIDH algorithm is used to secure inter-server communication" (Article Key contributions of this research) - SIDH, ABE-OD, inter-server authentication mechanisms implemented and benchmarked as cross-provider IAM mechanisms; "The Multi-Cloud Security Model brings inter-server verbal exchange, authentication integrity". (Article Introduction)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Concrete cross-provider authentication mechanisms empirically demonstrated → Yes.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>EV-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>"Identity Management, Authentication, and Access Control (PR.AA)" PR.AA-01 through PR.AA-06 establish authentication and access control requirements for identities, credentials, and access permissions (NIST, 2024, p.19); no adaptation for multi-cloud or cross-provider federation contexts provided.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>IAM addressed without multi-cloud federation elaboration; no cross-provider token validation or lifecycle synchronisation → Partial.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>PR.AA-01-06</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>EV-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>"to facilitate data sharing, concepts such as trust of federated identities and AC attributes need to be considered, and building that trust is paramount. In this document, it is assumed that trust and federated identities/attributes are already established, and further discussion on that topic will be considered in another document" (p. 7).</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Federated identity trust acknowledged but explicitly scoped out of this document; ABAC provides a single-provider IAM mechanism; no cross-provider federation mechanism defined; D6 = Partial.
+NOTE - Layer 1 (Normative Framework): Gap conclusions drawn from this row apply at framework level only; do not conflate with empirical or literature findings.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Secs. 2, 5.6, 5.7, 5.9 (federated identity and authorization)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>EV-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>"Providers like Google allow users to securely reuse their accounts to authenticate at other services by utilizing the protocols Open Authorization (OAuth)/OpenID Connect (OIDC). The alternative Federated Identity Management (FIM) protocol Security Assertion Markup Language (SAML) is typically used in research and education" (p. 196); FIMSM reference architecture uses ArchiMate to define six layers: External Layer, Business Service Layer, Business Layer, Application Service Layer, Application Layer, and Technical Service Layer for federated identity governance (p. 202).</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Explicit, structured federated IAM architecture with defined layers and governance components across SAML/OAuth/OIDC protocols; most detailed FIM reference model in corpus → D6 = Yes.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>EV-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>"Azure Arc integrates with Azure Active Directory for identity and access management (IAM), including role-based access control (RBAC)" (p.221); no cross-provider IAM federation governance mechanism proposed or evaluated.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>IAM addressed within single provider (Azure); no cross-provider identity federation mechanism → No.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Not double-coded</t>
         </is>
       </c>
     </row>
